--- a/data/credit_exposure_inputs.xlsx
+++ b/data/credit_exposure_inputs.xlsx
@@ -3758,7 +3758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3847,7 +3847,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>COL001</t>
+          <t>COL002</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -3862,12 +3862,12 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>F101</t>
+          <t>F102</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Receivables assignment</t>
+          <t>Commercial property</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -3886,176 +3886,180 @@
         </is>
       </c>
       <c r="I4" s="7" t="n">
-        <v>6000000</v>
+        <v>9300000</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>0.45</v>
+        <v>0.35</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>45473</v>
+        <v>45443</v>
       </c>
       <c r="L4" s="6" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>COL002</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>C001</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>20240715</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>COL004</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>C001</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>20250812</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>F102</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>Commercial property</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="9" t="inlineStr">
         <is>
           <t>First</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="9" t="inlineStr">
         <is>
           <t>GBP</t>
         </is>
       </c>
-      <c r="I5" s="7" t="n">
+      <c r="I5" s="11" t="n">
         <v>9300000</v>
       </c>
-      <c r="J5" s="8" t="n">
+      <c r="J5" s="12" t="n">
         <v>0.35</v>
       </c>
-      <c r="K5" s="6" t="n">
-        <v>45443</v>
-      </c>
-      <c r="L5" s="6" t="n"/>
+      <c r="K5" s="10" t="n">
+        <v>45930</v>
+      </c>
+      <c r="L5" s="10" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>COL003</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>C001</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>COL005</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>C001</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>20250812</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>F101</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>Receivables assignment</t>
-        </is>
-      </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>F103</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Standby letter of credit</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>First</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>GBP</t>
         </is>
       </c>
-      <c r="I6" s="11" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="J6" s="12" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="K6" s="10" t="n">
-        <v>45838</v>
-      </c>
-      <c r="L6" s="10" t="n"/>
+      <c r="I6" s="7" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="J6" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K6" s="6" t="n">
+        <v>45870</v>
+      </c>
+      <c r="L6" s="6" t="n">
+        <v>46265</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>COL004</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>C001</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>20250812</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>F102</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Commercial property</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>COL007</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>C001</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>20260904</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>F103</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>Standby letter of credit</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="9" t="inlineStr">
         <is>
           <t>First</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="9" t="inlineStr">
         <is>
           <t>GBP</t>
         </is>
       </c>
-      <c r="I7" s="7" t="n">
-        <v>9300000</v>
-      </c>
-      <c r="J7" s="8" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="K7" s="6" t="n">
-        <v>45930</v>
-      </c>
-      <c r="L7" s="6" t="n"/>
+      <c r="I7" s="11" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="J7" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K7" s="10" t="n">
+        <v>46235</v>
+      </c>
+      <c r="L7" s="10" t="n">
+        <v>46630</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>COL005</t>
+          <t>COL008</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -4065,17 +4069,17 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>20250812</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>F103</t>
+          <t>F105</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Standby letter of credit</t>
+          <t>Vehicle fleet charge</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -4094,42 +4098,40 @@
         </is>
       </c>
       <c r="I8" s="7" t="n">
-        <v>1500000</v>
+        <v>900000</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>45870</v>
-      </c>
-      <c r="L8" s="6" t="n">
-        <v>46265</v>
-      </c>
+        <v>46173</v>
+      </c>
+      <c r="L8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>COL006</t>
+          <t>COL010</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>C001</t>
+          <t>C002</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20250310</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>F101</t>
+          <t>F202</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>Receivables assignment</t>
+          <t>Cash deposit</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
@@ -4148,94 +4150,92 @@
         </is>
       </c>
       <c r="I9" s="11" t="n">
-        <v>6000000</v>
+        <v>2500000</v>
       </c>
       <c r="J9" s="12" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="K9" s="10" t="n">
-        <v>46203</v>
+        <v>45717</v>
       </c>
       <c r="L9" s="10" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>COL007</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>C001</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>20260904</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>F103</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>Standby letter of credit</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>COL012</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>C002</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>20260815</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>F202</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>Cash deposit</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" s="9" t="inlineStr">
         <is>
           <t>First</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H10" s="9" t="inlineStr">
         <is>
           <t>GBP</t>
         </is>
       </c>
-      <c r="I10" s="7" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="J10" s="8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K10" s="6" t="n">
+      <c r="I10" s="11" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="J10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="10" t="n">
         <v>46235</v>
       </c>
-      <c r="L10" s="6" t="n">
-        <v>46630</v>
-      </c>
+      <c r="L10" s="10" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>COL008</t>
+          <t>COL013</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>C001</t>
+          <t>C002</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260815</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>F105</t>
+          <t>F203</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Vehicle fleet charge</t>
+          <t>Commercial property</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -4254,45 +4254,45 @@
         </is>
       </c>
       <c r="I11" s="7" t="n">
-        <v>900000</v>
+        <v>5400000</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>0.5</v>
+        <v>0.35</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="L11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>COL009</t>
+          <t>COL014</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>C002</t>
+          <t>C003</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>20250310</t>
+          <t>20260620</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>F201</t>
+          <t>F301</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>Inventory charge</t>
+          <t>Commercial property</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>Floating</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
@@ -4306,306 +4306,46 @@
         </is>
       </c>
       <c r="I12" s="11" t="n">
-        <v>3600000</v>
+        <v>4000000</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>0.6</v>
+        <v>0.35</v>
       </c>
       <c r="K12" s="10" t="n">
-        <v>45716</v>
+        <v>46142</v>
       </c>
       <c r="L12" s="10" t="n"/>
     </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>COL010</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>C002</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>20250310</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>F202</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Cash deposit</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>First</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="n">
-        <v>2500000</v>
-      </c>
-      <c r="J13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="6" t="n">
-        <v>45717</v>
-      </c>
-      <c r="L13" s="6" t="n"/>
-    </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>COL011</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>C002</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>20260815</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>F201</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>Inventory charge</t>
-        </is>
-      </c>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>Floating</t>
-        </is>
-      </c>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>First</t>
-        </is>
-      </c>
-      <c r="H14" s="9" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="I14" s="11" t="n">
-        <v>3600000</v>
-      </c>
-      <c r="J14" s="12" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K14" s="10" t="n">
-        <v>46203</v>
-      </c>
-      <c r="L14" s="10" t="n"/>
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>Every collateral row belongs to a facility. Not every facility has one: an overdraft or card is typically unsecured, a property loan is not.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>COL012</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>C002</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>20260815</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>F202</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>Cash deposit</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>First</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="I15" s="7" t="n">
-        <v>2500000</v>
-      </c>
-      <c r="J15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="6" t="n">
-        <v>46235</v>
-      </c>
-      <c r="L15" s="6" t="n"/>
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>A facility with no row here is unsecured and takes the full unsecured LGD from the facility sheet.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>COL013</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>C002</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>20260815</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>F203</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>Commercial property</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>First</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="n">
-        <v>5400000</v>
-      </c>
-      <c r="J16" s="8" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="K16" s="6" t="n">
-        <v>46234</v>
-      </c>
-      <c r="L16" s="6" t="n"/>
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>One collateral item per facility at most. Charge rank is retained for context but there is no second charge in this dataset.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>COL014</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>C003</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>20260620</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>F301</t>
-        </is>
-      </c>
-      <c r="E17" s="9" t="inlineStr">
-        <is>
-          <t>Commercial property</t>
-        </is>
-      </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="G17" s="9" t="inlineStr">
-        <is>
-          <t>First</t>
-        </is>
-      </c>
-      <c r="H17" s="9" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="I17" s="11" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="J17" s="12" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="K17" s="10" t="n">
-        <v>46142</v>
-      </c>
-      <c r="L17" s="10" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>Every collateral row belongs to a facility. Not every facility has one: an overdraft or card is typically unsecured, a property loan is not.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t>A facility with no row here is unsecured and takes the full unsecured LGD from the facility sheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t>One collateral item per facility at most. Charge rank is retained for context but there is no second charge in this dataset.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>Haircut % is the discount applied before collateral counts towards recovery. Illustrative POC assumptions, not bank policy.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>Expiry date is blank for collateral that does not expire, such as property. Collateral expiring before the facility matures should not be relied on.</t>
         </is>
